--- a/Farm/Assets/Configs/llm_settings.xlsx
+++ b/Farm/Assets/Configs/llm_settings.xlsx
@@ -94,19 +94,19 @@
     <t>DeepSeek</t>
   </si>
   <si>
-    <t>sk-88310d74635747c38833c53f24ef02e7</t>
+    <t>sk-b84c42ba9d1042af9b165880c0306d61</t>
   </si>
   <si>
     <t>https://api.deepseek.com</t>
   </si>
   <si>
-    <t>deepseek-reasoner</t>
+    <t>deepseek-chat</t>
   </si>
   <si>
     <t>true</t>
   </si>
   <si>
-    <t>DeepSeek R1 推理模型</t>
+    <t>DeepSeek V3</t>
   </si>
 </sst>
 </file>
